--- a/flaskbackend/centercost_data/2024년7월.xlsx
+++ b/flaskbackend/centercost_data/2024년7월.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="271">
   <si>
     <t>코스트센터코드</t>
   </si>
@@ -827,9 +827,6 @@
   </si>
   <si>
     <t>(제)외주가공비-원자재</t>
-  </si>
-  <si>
-    <t>총비용</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E918"/>
+  <dimension ref="A1:E917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1289,7 +1286,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>535166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2037,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="E50">
-        <v>820861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2445,7 +2442,7 @@
         <v>145</v>
       </c>
       <c r="E74">
-        <v>229144920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2632,7 +2629,7 @@
         <v>100</v>
       </c>
       <c r="E85">
-        <v>217782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4145,7 +4142,7 @@
         <v>189</v>
       </c>
       <c r="E174">
-        <v>251386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4434,7 +4431,7 @@
         <v>189</v>
       </c>
       <c r="E191">
-        <v>12136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4604,7 +4601,7 @@
         <v>189</v>
       </c>
       <c r="E201">
-        <v>2037108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4893,7 +4890,7 @@
         <v>189</v>
       </c>
       <c r="E218">
-        <v>533034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5471,7 +5468,7 @@
         <v>189</v>
       </c>
       <c r="E252">
-        <v>1001235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -6049,7 +6046,7 @@
         <v>189</v>
       </c>
       <c r="E286">
-        <v>62056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6219,7 +6216,7 @@
         <v>219</v>
       </c>
       <c r="E296">
-        <v>3195087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -6270,7 +6267,7 @@
         <v>189</v>
       </c>
       <c r="E299">
-        <v>1448196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -6355,7 +6352,7 @@
         <v>219</v>
       </c>
       <c r="E304">
-        <v>48725359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -6406,7 +6403,7 @@
         <v>189</v>
       </c>
       <c r="E307">
-        <v>2229247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -6508,7 +6505,7 @@
         <v>219</v>
       </c>
       <c r="E313">
-        <v>52210485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -6542,7 +6539,7 @@
         <v>189</v>
       </c>
       <c r="E315">
-        <v>1918213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -6661,7 +6658,7 @@
         <v>219</v>
       </c>
       <c r="E322">
-        <v>17321869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -6712,7 +6709,7 @@
         <v>189</v>
       </c>
       <c r="E325">
-        <v>3550983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6797,7 +6794,7 @@
         <v>219</v>
       </c>
       <c r="E330">
-        <v>10532548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6831,7 +6828,7 @@
         <v>189</v>
       </c>
       <c r="E332">
-        <v>36384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6950,7 +6947,7 @@
         <v>219</v>
       </c>
       <c r="E339">
-        <v>7004008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -7001,7 +6998,7 @@
         <v>189</v>
       </c>
       <c r="E342">
-        <v>254926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -7069,7 +7066,7 @@
         <v>219</v>
       </c>
       <c r="E346">
-        <v>1734677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -7188,7 +7185,7 @@
         <v>219</v>
       </c>
       <c r="E353">
-        <v>157942927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -7222,7 +7219,7 @@
         <v>189</v>
       </c>
       <c r="E355">
-        <v>6076963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -7749,7 +7746,7 @@
         <v>100</v>
       </c>
       <c r="E386">
-        <v>79285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7987,7 +7984,7 @@
         <v>219</v>
       </c>
       <c r="E400">
-        <v>8270533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -8106,7 +8103,7 @@
         <v>219</v>
       </c>
       <c r="E407">
-        <v>2039064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -8157,7 +8154,7 @@
         <v>189</v>
       </c>
       <c r="E410">
-        <v>1405684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -8225,7 +8222,7 @@
         <v>219</v>
       </c>
       <c r="E414">
-        <v>44738740</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -8276,7 +8273,7 @@
         <v>189</v>
       </c>
       <c r="E417">
-        <v>5003845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -9330,7 +9327,7 @@
         <v>100</v>
       </c>
       <c r="E479">
-        <v>40657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -9772,7 +9769,7 @@
         <v>189</v>
       </c>
       <c r="E505">
-        <v>1211432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -10248,7 +10245,7 @@
         <v>100</v>
       </c>
       <c r="E533">
-        <v>790217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="1:5">
@@ -10418,7 +10415,7 @@
         <v>100</v>
       </c>
       <c r="E543">
-        <v>7735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -10537,7 +10534,7 @@
         <v>100</v>
       </c>
       <c r="E550">
-        <v>23039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -10656,7 +10653,7 @@
         <v>189</v>
       </c>
       <c r="E557">
-        <v>830161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -10843,7 +10840,7 @@
         <v>189</v>
       </c>
       <c r="E568">
-        <v>378455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -11013,7 +11010,7 @@
         <v>189</v>
       </c>
       <c r="E578">
-        <v>201120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -11319,7 +11316,7 @@
         <v>189</v>
       </c>
       <c r="E596">
-        <v>750911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -11472,7 +11469,7 @@
         <v>189</v>
       </c>
       <c r="E605">
-        <v>323920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -11710,7 +11707,7 @@
         <v>100</v>
       </c>
       <c r="E619">
-        <v>158037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -12407,7 +12404,7 @@
         <v>189</v>
       </c>
       <c r="E660">
-        <v>855599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -12985,7 +12982,7 @@
         <v>189</v>
       </c>
       <c r="E694">
-        <v>97102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -13274,7 +13271,7 @@
         <v>219</v>
       </c>
       <c r="E711">
-        <v>24460681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="712" spans="1:5">
@@ -13529,7 +13526,7 @@
         <v>219</v>
       </c>
       <c r="E726">
-        <v>10568241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727" spans="1:5">
@@ -13580,7 +13577,7 @@
         <v>189</v>
       </c>
       <c r="E729">
-        <v>271489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -13665,7 +13662,7 @@
         <v>219</v>
       </c>
       <c r="E734">
-        <v>17295683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -13716,7 +13713,7 @@
         <v>189</v>
       </c>
       <c r="E737">
-        <v>1448197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -13835,7 +13832,7 @@
         <v>189</v>
       </c>
       <c r="E744">
-        <v>634558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745" spans="1:5">
@@ -13920,7 +13917,7 @@
         <v>219</v>
       </c>
       <c r="E749">
-        <v>1518109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750" spans="1:5">
@@ -14124,7 +14121,7 @@
         <v>189</v>
       </c>
       <c r="E761">
-        <v>582608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="762" spans="1:5">
@@ -15416,7 +15413,7 @@
         <v>219</v>
       </c>
       <c r="E837">
-        <v>2503085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:5">
@@ -15467,7 +15464,7 @@
         <v>189</v>
       </c>
       <c r="E840">
-        <v>58005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="841" spans="1:5">
@@ -15535,7 +15532,7 @@
         <v>219</v>
       </c>
       <c r="E844">
-        <v>27936288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845" spans="1:5">
@@ -15586,7 +15583,7 @@
         <v>189</v>
       </c>
       <c r="E847">
-        <v>792528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848" spans="1:5">
@@ -15654,7 +15651,7 @@
         <v>219</v>
       </c>
       <c r="E851">
-        <v>3383002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="852" spans="1:5">
@@ -15960,7 +15957,7 @@
         <v>219</v>
       </c>
       <c r="E869">
-        <v>8121212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="870" spans="1:5">
@@ -15994,7 +15991,7 @@
         <v>189</v>
       </c>
       <c r="E871">
-        <v>147748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="872" spans="1:5">
@@ -16181,7 +16178,7 @@
         <v>219</v>
       </c>
       <c r="E882">
-        <v>1865080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883" spans="1:5">
@@ -16777,14 +16774,6 @@
       </c>
       <c r="E917">
         <v>18100883</v>
-      </c>
-    </row>
-    <row r="918" spans="1:5">
-      <c r="D918" t="s">
-        <v>271</v>
-      </c>
-      <c r="E918">
-        <v>7872654662</v>
       </c>
     </row>
   </sheetData>
